--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.36374926805361</v>
+        <v>10.78410925605871</v>
       </c>
       <c r="D2" t="n">
-        <v>66.53334195307674</v>
+        <v>10.81166806737497</v>
       </c>
       <c r="E2" t="n">
-        <v>14.69094779767433</v>
+        <v>2.387279017122079</v>
       </c>
       <c r="F2" t="n">
-        <v>15.83984112960682</v>
+        <v>2.573974183561109</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.19766652521226</v>
+        <v>3.932120810346993</v>
       </c>
       <c r="D3" t="n">
-        <v>24.37906041743091</v>
+        <v>3.961597317832523</v>
       </c>
       <c r="E3" t="n">
-        <v>14.69094779767433</v>
+        <v>2.387279017122079</v>
       </c>
       <c r="F3" t="n">
-        <v>15.83984112960682</v>
+        <v>2.573974183561109</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>67.2328193672695</v>
+        <v>10.92533314718129</v>
       </c>
       <c r="D4" t="n">
-        <v>66.05993275841989</v>
+        <v>10.73473907324323</v>
       </c>
       <c r="E4" t="n">
-        <v>14.69094779767433</v>
+        <v>2.387279017122079</v>
       </c>
       <c r="F4" t="n">
-        <v>15.83984112960682</v>
+        <v>2.573974183561109</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.77754821498458</v>
+        <v>9.063851584934994</v>
       </c>
       <c r="D5" t="n">
-        <v>54.21738213000638</v>
+        <v>8.810324596126037</v>
       </c>
       <c r="E5" t="n">
-        <v>14.69094779767433</v>
+        <v>2.387279017122079</v>
       </c>
       <c r="F5" t="n">
-        <v>15.83984112960682</v>
+        <v>2.573974183561109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.47625449881852</v>
+        <v>5.92739135605801</v>
       </c>
       <c r="D6" t="n">
-        <v>36.30554533584638</v>
+        <v>5.899651117075036</v>
       </c>
       <c r="E6" t="n">
-        <v>14.69094779767433</v>
+        <v>2.387279017122079</v>
       </c>
       <c r="F6" t="n">
-        <v>15.83984112960682</v>
+        <v>2.573974183561109</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.53617095768695</v>
+        <v>6.749627780624129</v>
       </c>
       <c r="D7" t="n">
-        <v>28.5954705339385</v>
+        <v>4.646763961765005</v>
       </c>
       <c r="E7" t="n">
-        <v>14.69094779767433</v>
+        <v>2.387279017122079</v>
       </c>
       <c r="F7" t="n">
-        <v>15.83984112960682</v>
+        <v>2.573974183561109</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.3940848977451</v>
+        <v>7.539038795883578</v>
       </c>
       <c r="D8" t="n">
-        <v>46.69466703261148</v>
+        <v>7.587883392799366</v>
       </c>
       <c r="E8" t="n">
-        <v>14.69094779767433</v>
+        <v>2.387279017122079</v>
       </c>
       <c r="F8" t="n">
-        <v>15.83984112960682</v>
+        <v>2.573974183561109</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
